--- a/ids_expansion_module.xlsx
+++ b/ids_expansion_module.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brad.parker/projects/SystemSurveyor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAA2559-FE7A-B340-AD24-AF0C532BDC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344B25E8-A831-F342-8282-AF87C193956C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33400" yWindow="2180" windowWidth="34560" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Element Profiles" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="89">
   <si>
     <t>Export date: Jun 29, 2026</t>
   </si>
@@ -268,6 +268,39 @@
   <si>
     <t>BE32</t>
   </si>
+  <si>
+    <t>QX61 BSP RS-485 Adapter</t>
+  </si>
+  <si>
+    <t>QX51 BSP Sensor Adapter</t>
+  </si>
+  <si>
+    <t>QX61</t>
+  </si>
+  <si>
+    <t>QX51</t>
+  </si>
+  <si>
+    <t>Addressable Loop</t>
+  </si>
+  <si>
+    <t>https://www.verkada.com/alarms/addressable-sensor-system/</t>
+  </si>
+  <si>
+    <t>BSP Product Page</t>
+  </si>
+  <si>
+    <t>QX61 Product Datasheet</t>
+  </si>
+  <si>
+    <t>QX51 Product Datasheet</t>
+  </si>
+  <si>
+    <t>https://docs.verkada.com/docs/QX61-BSP-RS-485-adapter-datasheet.pdf</t>
+  </si>
+  <si>
+    <t>https://docs.verkada.com/docs/QX51-BSP-sensor-adapter-datasheet.pdf</t>
+  </si>
 </sst>
 </file>
 
@@ -430,7 +463,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2">
       <alignment horizontal="center" vertical="center"/>
@@ -464,13 +497,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="4" applyFont="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -793,7 +830,7 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="15"/>
@@ -1297,9 +1334,9 @@
       <c r="SI1" s="15"/>
       <c r="SJ1" s="16"/>
     </row>
-    <row r="2" spans="3:504" ht="200" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:504" ht="200" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="2"/>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="15"/>
@@ -1803,7 +1840,7 @@
       <c r="SI2" s="15"/>
       <c r="SJ2" s="16"/>
     </row>
-    <row r="3" spans="3:504" ht="19" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:504" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1850,12 @@
       <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="F3" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>79</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2313,7 +2354,7 @@
       <c r="SI3" s="3"/>
       <c r="SJ3" s="3"/>
     </row>
-    <row r="4" spans="3:504" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:504" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="11" t="s">
         <v>6</v>
       </c>
@@ -2323,8 +2364,12 @@
       <c r="E4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -4337,8 +4382,12 @@
       <c r="E6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -4845,8 +4894,12 @@
       <c r="E7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
@@ -5353,8 +5406,12 @@
       <c r="E8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -7367,8 +7424,12 @@
       <c r="E10" s="5">
         <v>349</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="F10" s="5">
+        <v>199</v>
+      </c>
+      <c r="G10" s="5">
+        <v>129</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -11397,8 +11458,12 @@
       <c r="E14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="F14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -14941,7 +15006,7 @@
       <c r="SI20" s="7"/>
       <c r="SJ20" s="7"/>
     </row>
-    <row r="21" spans="3:504" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:504" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C21" s="11"/>
       <c r="D21" t="s">
         <v>35</v>
@@ -14949,8 +15014,12 @@
       <c r="E21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="F21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
@@ -15457,8 +15526,12 @@
       <c r="E22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="F22" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
@@ -15965,8 +16038,12 @@
       <c r="E23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="F23" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
@@ -16465,7 +16542,7 @@
       <c r="SI23" s="8"/>
       <c r="SJ23" s="8"/>
     </row>
-    <row r="24" spans="3:504" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:504" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C24" s="13"/>
       <c r="D24" s="6" t="s">
         <v>41</v>
@@ -16473,8 +16550,12 @@
       <c r="E24" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="F24" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
@@ -16973,7 +17054,7 @@
       <c r="SI24" s="9"/>
       <c r="SJ24" s="9"/>
     </row>
-    <row r="25" spans="3:504" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:504" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C25" s="11" t="s">
         <v>34</v>
       </c>
